--- a/docs/cadrage/Lundi/equipe-27-sprint-backlog-v1.0.xlsx
+++ b/docs/cadrage/Lundi/equipe-27-sprint-backlog-v1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flore\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flore\Documents\APOCALIPSSI\IPSSI_APOCAL_KIT\docs\cadrage\Lundi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574DA26B-C2D4-4EE9-8111-23E3F80487C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0DFA1D-E683-487D-A23C-88B8BD90663E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -396,9 +396,6 @@
     <t>Florent NGOR</t>
   </si>
   <si>
-    <t>Hady BALDE</t>
-  </si>
-  <si>
     <t>Développer la création de compte</t>
   </si>
   <si>
@@ -452,6 +449,9 @@
   <si>
     <t xml:space="preserve">Diana MARGARIAN, Florent NGOR, Hady BALDE, Denis URGEL,
 Mohammed EL KADDOURI, Fatma BOUZID  </t>
+  </si>
+  <si>
+    <t>Mostapha Bachir ADDI</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1192,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1200,7 +1200,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1208,7 +1208,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
@@ -1306,7 +1306,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1314,7 +1314,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1381,10 +1381,10 @@
         <v>49</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" s="21">
         <v>3</v>
@@ -1404,10 +1404,10 @@
         <v>51</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" s="21">
         <v>2</v>
@@ -1427,10 +1427,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E22" s="21">
         <v>1</v>
@@ -1450,10 +1450,10 @@
         <v>53</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="21">
         <v>1</v>
@@ -1473,10 +1473,10 @@
         <v>55</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" s="24">
         <v>1</v>
@@ -1496,10 +1496,10 @@
         <v>56</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="24">
         <v>3</v>
@@ -1519,10 +1519,10 @@
         <v>57</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" s="24">
         <v>1</v>
@@ -1542,10 +1542,10 @@
         <v>58</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" s="24">
         <v>1</v>
@@ -1846,7 +1846,7 @@
         <v>107</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1857,7 +1857,7 @@
         <v>107</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1868,7 +1868,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1879,7 +1879,7 @@
         <v>107</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1890,7 +1890,7 @@
         <v>107</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1901,7 +1901,7 @@
         <v>107</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1912,7 +1912,7 @@
         <v>107</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1923,7 +1923,7 @@
         <v>107</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1934,7 +1934,7 @@
         <v>107</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1945,7 +1945,7 @@
         <v>107</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
